--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Systems Engineer SME</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VTG Defense</t>
+          <t>Devengine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.6</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Scala</t>
+          <t>EMR, Kinesis, Redshift, Azure, Databricks, BigQuery, Spark, Kafka, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e738969e8679aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9e77377ecd96f1b9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Databricks Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Devengine</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EMR, Kinesis, Redshift, Azure, Databricks, BigQuery, Spark, Kafka, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e77377ecd96f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e82684b0040295</t>
         </is>
       </c>
     </row>
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineering - Senior Engineer</t>
+          <t>Engineer IV, AI &amp; Digital Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
+          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - NBA</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
+          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Production Operations Engineer</t>
+          <t>Software Engineering - Senior Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, Snowflake, Oracle, MySQL, DynamoDB, Splunk</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84465101ecfed6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Federal Home Loan Banks Office of Finance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
+          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - NBA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
+          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
+          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Architect / Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d30d040cab4dde</t>
+          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
+          <t>Sr. Salesforce Architect / Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d30d040cab4dde</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Azure)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Morgantown, WV, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
+          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sperry Rail</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
+          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Data Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675b9b533569f997</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,94 +1091,94 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee3bddf93c206b</t>
+          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08961c31c3764f09</t>
+          <t>https://www.indeed.com/viewjob?jk=675b9b533569f997</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Sperry Rail</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0a4f0fdf890593</t>
+          <t>https://www.indeed.com/viewjob?jk=7aee3bddf93c206b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=08961c31c3764f09</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0a4f0fdf890593</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Itron</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, Scala, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d4ea92b3de4658c</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Berxi</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Berxi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CURE Auto Insurance</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Teichert Construction</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, MLOps</t>
+          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc7127badc11937</t>
+          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Co-Op, DevOps Engineer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40696df5eb2aec78</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Insights Delivery Finance (Hybrid - Seattle, WA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=304b246d7ce7389e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newmark</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Oracle, Tableau, CI/CD, Git, Datadog</t>
+          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb5062224932805</t>
+          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Newmark</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,19 +3051,19 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3076,52 +3076,52 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Spark, PySpark, Scala, NoSQL, ETL, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=dc92f44a3afb58a3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, NoSQL, ETL, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc92f44a3afb58a3</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Application Development Senior Advisor- Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, Jenkins, Maven, Jenkins, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d47b6a52f18e37f</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Developer Engineer in Testing</t>
+          <t>Application Development Senior Advisor- Hybrid</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
+          <t>AWS, Scala, Kafka, Oracle, Jenkins, Maven, Jenkins, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1d47b6a52f18e37f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Senior Software Developer Engineer in Testing</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SHAKTECH CORP</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Woodlawn, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f29600f2b8dc13</t>
+          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e82684b0040295</t>
+          <t>https://www.indeed.com/viewjob?jk=37f9cb4e7f9e0916</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — AI/ML Data Platforms</t>
+          <t>Sr Databricks Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T. Mims Corp.</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac713d0689b63faa</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e82684b0040295</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer IV, AI &amp; Digital Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>Vagaro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Data Lake Storage, GCP, Spark, PySpark, Scala, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
+          <t>https://www.indeed.com/viewjob?jk=44fc81c2d0a70c40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer — AI/ML Data Platforms</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>T. Mims Corp.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac713d0689b63faa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineering - Senior Engineer</t>
+          <t>Engineer IV, AI &amp; Digital Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
+          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Federal Home Loan Banks Office of Finance</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
+          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - NBA</t>
+          <t>Software Engineering - Senior Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Federal Home Loan Banks Office of Finance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
+          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - NBA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
+          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
+          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Architect / Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d30d040cab4dde</t>
+          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morgantown, WV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a7db885e08246b</t>
+          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
+          <t>Sr. Salesforce Architect / Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d30d040cab4dde</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Azure)</t>
+          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
+          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sperry Rail</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>Sperry Rail</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675b9b533569f997</t>
+          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sperry Rail</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee3bddf93c206b</t>
+          <t>https://www.indeed.com/viewjob?jk=675b9b533569f997</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08961c31c3764f09</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0a4f0fdf890593</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Berxi</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Database Architect</t>
+          <t>Senior Data Engineer, Berxi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, HBase, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ab183217fe971</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Cloud Database Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, GCP, HBase, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ab183217fe971</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Medallion Architecture, BigQuery, Spark, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8092575b540f4d54</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Guidewire Data Architect</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rockwoods Inc</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2d40a87f71d317</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Cloud Storage, Snowflake, Oracle, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff372041e842459</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Guidewire Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Rockwoods Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Redshift, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=5f2d40a87f71d317</t>
         </is>
       </c>
     </row>
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
         </is>
       </c>
     </row>
@@ -2661,29 +2661,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Azure Cloud Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d5577a89f311660</t>
+          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Newmark</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Newmark</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,42 +3076,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, NoSQL, ETL, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc92f44a3afb58a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,15 +3138,15 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,15 +3173,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Application Development Senior Advisor- Hybrid</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Scala, Kafka, Oracle, Jenkins, Maven, Jenkins, Git, Python, SQL</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d47b6a52f18e37f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Developer Engineer in Testing</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Clearing House Payments Company</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Kafka</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d369a229cb2f75b9</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,15 +3531,190 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Vital Services</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Oak Ridge, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Frontapp</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675b9b533569f997</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Senior Data Engineer, Berxi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Berxi</t>
+          <t>Cloud Database Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>AWS, RDS, GCP, HBase, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ab183217fe971</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Database Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, HBase, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ab183217fe971</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
@@ -1693,25 +1693,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
@@ -2253,25 +2253,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17d6ae908b8e7d72</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f458b7778293846f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d6afe51fc6e261a</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Newmark</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Newmark</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,15 +3208,15 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,15 +3243,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3610,111 +3610,6 @@
         </is>
       </c>
       <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Frontapp</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CURE Auto Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb452da16920d81</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Guidewire Data Architect</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rockwoods Inc</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2d40a87f71d317</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CURE Auto Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
@@ -2603,35 +2603,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Newmark</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2818,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Newmark</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,24 +3496,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3611,7 +3611,77 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Frontapp</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
           <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Quandary Consulting Group</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a82b38274b566db9</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CURE Auto Insurance</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2988,7 +2988,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, Cassandra, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c149b0229a30a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Solutions Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>Quandary Consulting Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a82b38274b566db9</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Solutions Consultant</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Quandary Consulting Group</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82b38274b566db9</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,12 +958,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Senior Associate - Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,38 +972,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
+          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Architect / Engineer</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d30d040cab4dde</t>
+          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
+          <t>Sr. Salesforce Architect / Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d30d040cab4dde</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Azure)</t>
+          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
+          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sperry Rail</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Sperry Rail</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Berxi</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Database Architect</t>
+          <t>Senior Data Engineer, Berxi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, HBase, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ab183217fe971</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Database Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>AWS, RDS, GCP, HBase, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6ab183217fe971</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CURE Auto Insurance</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
@@ -2253,25 +2253,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,52 +2621,52 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Newmark</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Newmark</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,24 +3531,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Solutions Consultant</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Quandary Consulting Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82b38274b566db9</t>
+          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Solutions Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>Quandary Consulting Group</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a82b38274b566db9</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3680,6 +3680,41 @@
         </is>
       </c>
       <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Frontapp</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,12 +748,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineering - Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Federal Home Loan Banks Office of Finance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, RDS, Scala, Kafka, Oracle, MySQL, MongoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8abb748a167939</t>
+          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - NBA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Federal Home Loan Banks Office of Finance</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - NBA</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
+          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
+          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Associate - Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,29 +941,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
+          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,46 +972,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
+          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Salesforce Architect / Engineer</t>
+          <t>Data Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Manhattan Beach, CA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Azure, Scala, Oracle, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d30d040cab4dde</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Sperry Rail</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
+          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Azure)</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sperry Rail</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Database Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, HBase, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ab183217fe971</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
@@ -1658,25 +1658,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Newmark</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Event Hubs, GCP, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecea5a726201bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
         </is>
       </c>
     </row>
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,24 +3566,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Solutions Consultant</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Quandary Consulting Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82b38274b566db9</t>
+          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Solutions Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>Quandary Consulting Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,85 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a82b38274b566db9</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Frontapp</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Integra Connect</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Berxi</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Berxi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
@@ -1658,25 +1658,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ab8998579dcc3a</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,52 +2656,52 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,24 +2901,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43bab62e6ea0712</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2fa28942f5a9923</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Solutions Consultant</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Quandary Consulting Group</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3715,76 +3715,6 @@
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a82b38274b566db9</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Frontapp</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CURE Auto Insurance</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,52 +2691,52 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,24 +2936,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Full Stack Developer - Java/ React</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3715,6 +3715,41 @@
         </is>
       </c>
       <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Frontapp</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Berxi</t>
+          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, SQL Server, NoSQL, ETL, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdcd811be7d4a19d</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CURE Auto Insurance</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Big Bridge Holdings, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,42 +2701,42 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b878c9ad00168635</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,102 +3086,102 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a41ffcb11e1749</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Java/ React</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,15 +3208,15 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aa25871e93c329</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3610,146 +3610,6 @@
         </is>
       </c>
       <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Frontapp</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer – Snowflake (Azure / Entra ID)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Integra Connect</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Time Travel, dbt, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7029dd2c0aa17f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Ashburn Consulting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
@@ -1658,25 +1658,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (With SRE Trajectory)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Big Bridge Holdings, Inc.</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, MongoDB, CI/CD, Jenkins</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e17a536e9381936</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,87 +2586,87 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer + Junior Architect</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c52bdf1b2f2d60</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3505,111 +3505,6 @@
         </is>
       </c>
       <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Frontapp</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
@@ -1658,25 +1658,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>FDE AI/ Solutions Architect (AI, Python/Data)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Azure, GCP, Spark, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c055ce9797102c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>FDE AI/ Solutions Architect (AI, Python/Data)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,112 +2586,112 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Azure, GCP, Spark, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ffa2bfcb22c9c8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,42 +2701,42 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior AI/ML Engineer (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, Lambda, S3, SQS, ECS, Azure, GCP, Spark, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=1075d7cc0d3e8b57</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior AI/ML Engineer (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, ECS, Azure, GCP, Spark, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb69f45b1c58c41</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,15 +2998,15 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,49 +3016,49 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,15 +3068,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3142,11 +3142,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,15 +3496,225 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Vital Services</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Oak Ridge, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Frontapp</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Delta Live Tables, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ea33155120cc34</t>
+          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate - Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,64 +871,64 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
+          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Azure, GCP, Hadoop, Impala, Spark, Scala</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=273dfb2fd34849a0</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,46 +937,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
+          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
+          <t>Data Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Azure)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Sperry Rail</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
+          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sperry Rail</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CURE Auto Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
@@ -1658,25 +1658,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>IT Analyst Senior</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=ad738591847ea39e</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FDE AI/ Solutions Architect (AI, Python/Data)</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Azure, GCP, Spark, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c055ce9797102c</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FDE AI/ Solutions Architect (AI, Python/Data)</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Azure, GCP, Spark, CI/CD</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ffa2bfcb22c9c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,42 +2701,42 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer (GenAI, AWS)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, Azure, GCP, Spark, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1075d7cc0d3e8b57</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer (GenAI, AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, Azure, GCP, Spark, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb69f45b1c58c41</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,102 +3051,102 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>FRONT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Frontapp</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,155 +3566,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>FRONT</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Frontapp</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ashburn Consulting</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c5c3ce3e81946d</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>IT Analyst Senior</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=ad738591847ea39e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IT Analyst Senior</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, Tableau, MLOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad738591847ea39e</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Associate, Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,52 +2656,52 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,24 +2901,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,59 +3051,59 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Frontapp</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,87 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>FRONT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0f3e6a0329e2b7</t>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,95 +678,95 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer IV, AI &amp; Digital Engineering</t>
+          <t>Quality Engineering (QE) Data Quality Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Engineer- Full Stack USA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer IV, AI &amp; Digital Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Federal Home Loan Banks Office of Finance</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
+          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - NBA</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
+          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
         </is>
       </c>
     </row>
@@ -823,20 +823,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Federal Home Loan Banks Office of Finance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
+          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>Senior Data Engineer - NBA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
+          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Senior Associate - Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,46 +937,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
+          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
+          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Azure)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sperry Rail</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
+          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>Data Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>Sperry Rail</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,102 +1161,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,147 +1326,147 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,54 +1476,54 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,102 +1651,102 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IT Analyst Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>CURE Auto Insurance</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, Tableau, MLOps</t>
+          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad738591847ea39e</t>
+          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>IT Analyst Senior</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ad738591847ea39e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Software Engineer II - Backend</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0091e3c3966a16</t>
+          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate, Analytics Engineer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, BigQuery, Snowflake, dbt, Tableau</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74f8cda1493a2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, Scala, Data Modeling</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba4ddae196475dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,112 +2691,112 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,42 +2806,42 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,112 +3076,112 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,19 +3191,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3212,11 +3212,11 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior AI Platform Security Engineer - Contract to Hire</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FRONT</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,157 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, dbt, Splunk, CI/CD, Terraform, Airflow</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afaa91243be013f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Allen Park, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>.NET Backend Developer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Inclusion Cloud</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Devengine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Azure, Data Factory</t>
+          <t>EMR, Kinesis, Redshift, Azure, Databricks, BigQuery, Spark, Kafka, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d356376aee9aed9</t>
+          <t>https://www.indeed.com/viewjob?jk=9e77377ecd96f1b9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Databricks Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Devengine</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EMR, Kinesis, Redshift, Azure, Databricks, BigQuery, Spark, Kafka, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e77377ecd96f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=37f9cb4e7f9e0916</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f9cb4e7f9e0916</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e82684b0040295</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Vagaro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Lake Storage, GCP, Spark, PySpark, Scala, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e82684b0040295</t>
+          <t>https://www.indeed.com/viewjob?jk=44fc81c2d0a70c40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer — AI/ML Data Platforms</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vagaro</t>
+          <t>T. Mims Corp.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Lake Storage, GCP, Spark, PySpark, Scala, SQL Server, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fc81c2d0a70c40</t>
+          <t>https://www.indeed.com/viewjob?jk=ac713d0689b63faa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — AI/ML Data Platforms</t>
+          <t>Quality Engineering (QE) Data Quality Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T. Mims Corp.</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac713d0689b63faa</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Quality Engineering (QE) Data Quality Engineer</t>
+          <t>Engineer- Full Stack USA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer- Full Stack USA</t>
+          <t>Engineer IV, AI &amp; Digital Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Perrysburg, OH, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer IV, AI &amp; Digital Engineering</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
+          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Federal Home Loan Banks Office of Finance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
+          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - NBA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Federal Home Loan Banks Office of Finance</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - NBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
+          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate - Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
+          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
+          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
+          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
+          <t>Data Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Azure)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Sperry Rail</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
+          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sperry Rail</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer Job</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Lancaster, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Full Stack Developer - Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US | JPMC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CURE Auto Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d8077cddaec91f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>IT Analyst Senior</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=ad738591847ea39e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IT Analyst Senior</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, Tableau, MLOps</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad738591847ea39e</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,129 +2386,129 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer II - Backend</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, Databricks, GCP, Scala, Kafka, ETL, CI/CD, Docker</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5500d6b30d337bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,42 +2806,42 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,102 +3121,102 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>US Mobile</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cfb69843b2db92</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Vital Services</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,155 +3636,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Allen Park, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>.NET Backend Developer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Inclusion Cloud</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vagaro</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Lake Storage, GCP, Spark, PySpark, Scala, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fc81c2d0a70c40</t>
+          <t>https://www.indeed.com/viewjob?jk=593e53f5fee30d60</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — AI/ML Data Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Mims Corp.</t>
+          <t>Vagaro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>AWS, RDS, Azure, Data Lake Storage, GCP, Spark, PySpark, Scala, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac713d0689b63faa</t>
+          <t>https://www.indeed.com/viewjob?jk=44fc81c2d0a70c40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Quality Engineering (QE) Data Quality Engineer</t>
+          <t>Senior Data Engineer — AI/ML Data Platforms</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>T. Mims Corp.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ac713d0689b63faa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer- Full Stack USA</t>
+          <t>Quality Engineering (QE) Data Quality Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Perrysburg, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer IV, AI &amp; Digital Engineering</t>
+          <t>Engineer- Full Stack USA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Engineer IV, AI &amp; Digital Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Federal Home Loan Banks Office of Finance</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
+          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - NBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Federal Home Loan Banks Office of Finance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
+          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - NBA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
+          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
+          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
+          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
+          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
+          <t>Senior Associate - Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
+          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Azure)</t>
+          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,207 +1091,207 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sperry Rail</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer Job</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Armstrong World Industries</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lancaster, PA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83106bef0df0d936</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Sperry Rail</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb01dfa6121864df</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,89 +1826,89 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,151 +1917,151 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IT Analyst Senior</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, Tableau, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad738591847ea39e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Full Stack Developer - Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Quality Insights</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,137 +2386,137 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,94 +2596,94 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GCP Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alchemy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,94 +2946,94 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cea1d8921bab123</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,172 +3121,172 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,332 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Vital Services</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Allen, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Vital Services</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Oak Ridge, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MAPFRE Insurance</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Webster, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>.NET Backend Developer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Inclusion Cloud</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Allen Park, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer — AI/ML Data Platforms</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vagaro</t>
+          <t>T. Mims Corp.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Lake Storage, GCP, Spark, PySpark, Scala, SQL Server, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, SQS, SNS, ECS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fc81c2d0a70c40</t>
+          <t>https://www.indeed.com/viewjob?jk=ac713d0689b63faa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — AI/ML Data Platforms</t>
+          <t>Quality Engineering (QE) Data Quality Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T. Mims Corp.</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac713d0689b63faa</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Quality Engineering (QE) Data Quality Engineer</t>
+          <t>Engineer- Full Stack USA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer- Full Stack USA</t>
+          <t>Engineer IV, AI &amp; Digital Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Perrysburg, OH, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer IV, AI &amp; Digital Engineering</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
+          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Federal Home Loan Banks Office of Finance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
+          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - NBA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Federal Home Loan Banks Office of Finance</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - NBA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
+          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
+          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate - Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
+          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>microsoft power platform developer architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Infotech Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=2175da23d4e89e3b</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Snowflake_DBT Developers</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Azure, Scala, Snowflake, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb81b67805de775</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>The Iowa Clinic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=977d8141140e0e6c</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sperry Rail</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6013a09b90a06810</t>
+          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,147 +1816,147 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,102 +2106,102 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14a4b8559fd52ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer - Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>doctronic</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Quality Insights</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Data Modeling</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff47e82bfc5817a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,94 +2666,94 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GCP Data Engineer / Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, Medallion Architecture, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b975b94e360553b7</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,52 +3006,52 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,24 +3286,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,59 +3366,59 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
+          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde9e1e8cee00e1c</t>
+          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Vital Services</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88e6aff03fdd859</t>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,24 +3846,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3891,77 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Kubernetes, SonarQube, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ef31c83a604594</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer — AI/ML Data Platforms</t>
+          <t>Quality Engineering (QE) Data Quality Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Mims Corp.</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, SQS, SNS, ECS</t>
+          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac713d0689b63faa</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Quality Engineering (QE) Data Quality Engineer</t>
+          <t>Engineer- Full Stack USA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer- Full Stack USA</t>
+          <t>Engineer IV, AI &amp; Digital Engineering</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Perrysburg, OH, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer IV, AI &amp; Digital Engineering</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
+          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Federal Home Loan Banks Office of Finance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
+          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - NBA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Federal Home Loan Banks Office of Finance</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - NBA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
+          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
+          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate - Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
+          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>microsoft power platform developer architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Infotech Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=2175da23d4e89e3b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>microsoft power platform developer architect</t>
+          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Infotech Solutions</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2175da23d4e89e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>The Iowa Clinic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=977d8141140e0e6c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
+          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Iowa Clinic</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977d8141140e0e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
+          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Azure)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Scala, Power BI, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0402f8984e68c388</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,104 +1501,104 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Infoverity</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,94 +1896,94 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Full Stack Developer - Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,54 +2141,54 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>doctronic</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2197,11 +2197,11 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, ECS, IAM, RDS, Databricks, Snowflake</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a1804955dab550</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ab38c6d425e57a4d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2393,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2407,151 +2407,151 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ae117696ae2b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49708d8edca6e04</t>
+          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7bc23cafde3de00</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a04069d3f3584ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f02fd8499365382</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>City of Industry, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,137 +2596,137 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3984756cdac147</t>
+          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b605dce7b0600d93</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e82c34131ee2765</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full Stack .NET Developer</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22bf48116516e1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,42 +2761,42 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,102 +2841,102 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,42 +3016,42 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=00eec4e6432a7078</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,94 +3331,94 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42e7817a8874a099</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e748964b56e3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0101421529dd218</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer with scrum skills- Onsite</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,190 +3706,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=817bdac6a5468393</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>MAPFRE Insurance</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Webster, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>.NET Backend Developer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Inclusion Cloud</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Allen Park, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,35 +783,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - NBA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6252cdef37affd1</t>
+          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515f3bff52abe8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f887668cf9aaf20f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate - Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Spark, Scala, Kafka, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd674fe067dfdd34</t>
+          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform System Administrator III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Arden Hills, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,77 +941,77 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Delta Live Tables, Google Cloud Platform, GCP, Spark, PySpark, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8706228d4894a66</t>
+          <t>https://www.indeed.com/viewjob?jk=62388f603bbe60a4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Associate - Cloud Platform Engineer</t>
+          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce955d83d523351c</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>microsoft power platform developer architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Infotech Solutions</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, NoSQL, Power BI</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2175da23d4e89e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer 3 - TS clearance required - Wash DC area</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2b94a977d2119</t>
+          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Full stack Java Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e89b177e72a80</t>
+          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f12b1ea10022a2</t>
+          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6bc74fdfdbbca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Allentown, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c5bf2319077628</t>
+          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=603c61b7cc5fe1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>The Iowa Clinic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Allentown, PA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7340ebb5e99bf41f</t>
+          <t>https://www.indeed.com/viewjob?jk=977d8141140e0e6c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Full stack Java Developer</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bb7609c20e949e</t>
+          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Iowa Clinic</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977d8141140e0e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Property Claims - Infrastructure, Data, and Automation Engineer Senior Consultant - Remote</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Cloud Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364aa26c62c49e99</t>
+          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>Sr. Specialist, AI CRM Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,77 +1396,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=125902545a13a43c</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Specialist, AI CRM Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2323a1df671308a</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data and Integration Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Platte River Power Authority</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,147 +1746,147 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Consultant, Data Engineer | Databricks</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data and Integration Developer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Platte River Power Authority</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Collins, CO, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bef94e108ffe967</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Infoverity</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dublin, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f507aa8170f412</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c80455e75f43f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Consultant, Data Engineer | Databricks</t>
+          <t>Full Stack Developer - Advanced | Columbus, US</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87fd62c345b8469e</t>
+          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,94 +2036,94 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Advanced | Columbus, US</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Vertex AI, Scala, Kafka, NoSQL</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=865f8a104cb006d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>American Tire Distributors</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Spark, Scala, Kafka, Snowflake, DynamoDB, NoSQL, MLOps</t>
+          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=766cfaa008af94ec</t>
+          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Mossville, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
+          <t>https://www.indeed.com/viewjob?jk=ab38c6d425e57a4d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>SelectQuote</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior AI/ML Full Stack Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>Da Vinci Software</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Development Engineer II - C# and Azure Cloud</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,129 +2281,129 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab38c6d425e57a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SelectQuote</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, SQL Server, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23f04a50e41c3404</t>
+          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior AI/ML Full Stack Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Da Vinci Software</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Azure DevOps</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5909a21a93a5cfb9</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - C# and Azure Cloud</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=819e3084b1b0c608</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Economic Data System Engineer/Sr. Economic Data System Engineer-ITDDPED</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, ELT</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a32b2285f6e0f19</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Network and Security Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CSIK Consulting</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3010d5b2a695909</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>UC Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,42 +2621,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,94 +2701,94 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, Tableau</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00eec4e6432a7078</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Analytics Engineer - Direct Hire - 4 days onsite</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28383d93819eb75f</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,155 +3566,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>.NET Backend Developer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Inclusion Cloud</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Allen Park, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>

--- a/results/job_matches_2026-08-21.xlsx
+++ b/results/job_matches_2026-08-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Databricks Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Devengine</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EMR, Kinesis, Redshift, Azure, Databricks, BigQuery, Spark, Kafka, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e77377ecd96f1b9</t>
+          <t>https://www.indeed.com/viewjob?jk=37f9cb4e7f9e0916</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f9cb4e7f9e0916</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e82684b0040295</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Databricks Engineer</t>
+          <t>Senior Data Engineer (Analytics)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e82684b0040295</t>
+          <t>https://www.indeed.com/viewjob?jk=593e53f5fee30d60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Analytics)</t>
+          <t>Quality Engineering (QE) Data Quality Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593e53f5fee30d60</t>
+          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Quality Engineering (QE) Data Quality Engineer</t>
+          <t>Engineer- Full Stack USA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, Databricks, BigQuery, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9b2b6cddab662d6</t>
+          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer- Full Stack USA</t>
+          <t>Engineer IV, AI &amp; Digital Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Perrysburg, OH, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feaf58186fd25df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer IV, AI &amp; Digital Engineering</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3046d8552c476c9</t>
+          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Federal Home Loan Banks Office of Finance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d39ba4a5a320f</t>
+          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Microsoft Fabric</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Federal Home Loan Banks Office of Finance</t>
+          <t>Bilzin Sumberg Baena Price &amp; Axelrod LLP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Dataflow, Spark, PySpark</t>
+          <t>S3, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f5e922ac42e38d</t>
+          <t>https://www.indeed.com/viewjob?jk=371409082795e582</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Iowa Clinic</t>
+          <t>LegitScript</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977d8141140e0e6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac58242095324ac</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
+          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>The Iowa Clinic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
+          <t>https://www.indeed.com/viewjob?jk=977d8141140e0e6c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Solution Architect (Java, Cloud &amp; AI) - FTE / Hybrid</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Databricks, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=cff991eacc7c642b</t>
         </is>
       </c>
     </row>
@@ -1413,52 +1413,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer 2 - TS required - Washington DC area</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bow Wave LLC</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e7b1c586e6a4d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 2 - TS required - Washington DC area</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Bow Wave LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
+          <t>https://www.indeed.com/viewjob?jk=de40e05b432ea8b8</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc84ba97f996450</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d2db7b4c8d89f8</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
+          <t>https://www.indeed.com/viewjob?jk=74f4fee2cc3d811b</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ad9782930201d7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Finance Solutions, Google Cloud Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
+          <t>https://www.indeed.com/viewjob?jk=61bab526ed5bb2fe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Finance Solutions, Google Cloud Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Oracle, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9c9dcf629a4f65</t>
+          <t>https://www.indeed.com/viewjob?jk=c94336bbf2aab76d</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Software Engineer II, Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Credit Acceptance</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=39dcfd9f2966d672</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Engineer; Platform Analytics (Contract)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vervint</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8209ae3042e1b9a9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, IT Enterprise Data Solutions</t>
+          <t>Cloud Engineer; Platform Analytics (Contract)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>Vervint</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, S3, SQS, IAM, RDS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6c1bba3066513c</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0847cb6bf1b0e8</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, EMR, Kinesis, S3, RDS, Spark, Scala, PostgreSQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1eabd20620b211</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>7-Eleven</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef1c00bbfcfa5af</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Puig</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
+          <t>https://www.indeed.com/viewjob?jk=da2726835c895c54</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Tire Distributors</t>
+          <t>Puig</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, BigQuery, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL, Talend</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279caace7a880560</t>
+          <t>https://www.indeed.com/viewjob?jk=b295c5eb1d7771ed</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Full stack Java / AWS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mossville, IL, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab38c6d425e57a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=648c04000182f970</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Denodo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Flowserve</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, dbt, Tableau, CI/CD</t>
+          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db0ab6465cbf1ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer Denodo</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Flowserve</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87d344718e073fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTi Technology Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae435ef03aa1b3c0</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>QA Automation Engineer II, Officer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LTi Technology Solutions</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaa3af91b36b2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>QA Automation Engineer II, Officer</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, NoSQL, Talend, CI/CD, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d73747fd9aafef8</t>
+          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b64578e43ebdc</t>
+          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Network and Security Architect</t>
+          <t>Sr Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CSIK Consulting</t>
+          <t>Pilot Flying J</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ffec3454941064</t>
+          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Golden State</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ECS, RDS, Google Cloud Platform, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9514cb3d03b95a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179685542a7cf944</t>
+          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>UC Engineer II</t>
+          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f73c46ab8bbd18</t>
+          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Engineer, Data Engineering</t>
+          <t>AI Engineer/DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pilot Flying J</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a70d5a50e3bc2a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analyst, Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Golden State</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d156f80ddb5ea3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340f3540cd359821</t>
+          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Advanced Data Integration &amp; Cloud Solutions</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, ETL, Python, SQL</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1d4ee2bfb7f383</t>
+          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Engineer/DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, Splunk, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e19bdfcdfa54e3</t>
+          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala</t>
+          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8382e0121c068a19</t>
+          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cf52c60da7e9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Slavic401K</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e67652360d9f4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630a35e9cb636a94</t>
+          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7177817f699c500d</t>
+          <t>https://www.indeed.com/viewjob?jk=320dcd4f927cb250</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Quality Engineering (QE) Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Amida Technology Solutions</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96181d258407853f</t>
+          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect - WORK FROM HOME - SELECT US STATES ONLY</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Slavic401K</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,42 +3041,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df39dd0505c33d32</t>
+          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer - Vehicle Connectivity &amp; mobility (VC&amp;M)</t>
+          <t>Associate, Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f272fafe4eb2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Quality Engineering (QE) Engineer</t>
+          <t>Data Anchor</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Amida Technology Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Power BI, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a7f8ff4391f120</t>
+          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6db805cce62a3db2</t>
+          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Chiesi Farmaceutici S.p.A.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06fd6810514e5491</t>
+          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Anchor</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Apex, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Vertex AI, Hadoop, Spark, Kafka, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db1969fc986c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Data Engineer - GCP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45eef8c152b64a60</t>
+          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer, Marketing Sciences</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Chiesi Farmaceutici S.p.A.</t>
+          <t>SimplePractice</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, ETL, dbt, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d407207abb7498</t>
+          <t>https://www.indeed.com/viewjob?jk=4a341479dc01b56f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f4a26c4099d210</t>
+          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>.NET Backend Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Inclusion Cloud</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c305ad2167ff6fd</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GCP</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, dbt, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91f4d38456c03dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Agent Experience Platform</t>
+          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73664071b95987ff</t>
+          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>.NET Backend Developer</t>
+          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,120 +3461,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9d1b0d1d29e0d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Allen Park, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb7a428029c6a47</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer – CI/CD &amp; Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24a6d7aaf0bcba34</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - CI/CD and Software Development Tools</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c07d3c81a46d8e9a</t>
         </is>
